--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -39,31 +39,34 @@
     <t xml:space="preserve">San Rafael</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empedrado</t>
+    <t xml:space="preserve">Yerbas Buenas</t>
   </si>
   <si>
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Claro</t>
+    <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
     <t xml:space="preserve">Retiro</t>
@@ -72,54 +75,51 @@
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Hualañé</t>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
   </si>
   <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
+    <t xml:space="preserve">Teno</t>
   </si>
   <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">Parral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curepto</t>
   </si>
   <si>
-    <t xml:space="preserve">Parral</t>
+    <t xml:space="preserve">Linares</t>
   </si>
   <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">Linares</t>
+    <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">Curicó</t>
   </si>
   <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Constitución</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -559,16 +559,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7105</v>
+        <v>7110</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>60.84</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="3">
@@ -576,16 +576,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7110</v>
+        <v>7105</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>56.4</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="4">
@@ -596,13 +596,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7107</v>
+        <v>7203</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52.76</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="5">
@@ -613,13 +613,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7203</v>
+        <v>7106</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>52.42</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="6">
@@ -630,13 +630,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7106</v>
+        <v>7104</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>50.41</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="7">
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7104</v>
+        <v>7107</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>47.03</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="8">
@@ -664,13 +664,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7306</v>
+        <v>7408</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44.89</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="9">
@@ -681,13 +681,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7408</v>
+        <v>7306</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>41.52</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40.39</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="11">
@@ -715,13 +715,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7305</v>
+        <v>7108</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>38.22</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="12">
@@ -732,13 +732,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7108</v>
+        <v>7305</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37.42</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="13">
@@ -749,13 +749,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7405</v>
+        <v>7302</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>35.78</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="14">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7402</v>
+        <v>7405</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34.56</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="15">
@@ -783,13 +783,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7309</v>
+        <v>7402</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34.41</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="16">
@@ -800,13 +800,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7302</v>
+        <v>7303</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34.3</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="17">
@@ -817,13 +817,13 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7101</v>
+        <v>7309</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>33.39</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="18">
@@ -834,13 +834,13 @@
         <v>21</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7403</v>
+        <v>7202</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>32.5</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="19">
@@ -851,13 +851,13 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7303</v>
+        <v>7403</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>31.77</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="20">
@@ -868,13 +868,13 @@
         <v>23</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7406</v>
+        <v>7307</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.7</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="21">
@@ -885,13 +885,13 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7308</v>
+        <v>7101</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>31.65</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="22">
@@ -902,13 +902,13 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7307</v>
+        <v>7308</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>30.41</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="23">
@@ -919,13 +919,13 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7202</v>
+        <v>7406</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>30.4</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30.33</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="25">
@@ -953,13 +953,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7103</v>
+        <v>7404</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>30.21</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="26">
@@ -970,13 +970,13 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7404</v>
+        <v>7103</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>29.95</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="27">
@@ -987,13 +987,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7304</v>
+        <v>7401</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>28.05</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="28">
@@ -1004,13 +1004,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7401</v>
+        <v>7304</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>27.82</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="29">
@@ -1021,13 +1021,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7301</v>
+        <v>7201</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>26.67</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="30">
@@ -1038,13 +1038,13 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7201</v>
+        <v>7301</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>25.29</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>22.54</v>
+        <v>10.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:19</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>29.37</v>
+        <v>293.73</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27.82</v>
+        <v>278.23</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>26.62</v>
+        <v>266.17</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25.33</v>
+        <v>253.35</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>24.68</v>
+        <v>246.79</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.42</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.99</v>
+        <v>219.86</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>21.32</v>
+        <v>213.22</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.29</v>
+        <v>192.89</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>18.15</v>
+        <v>181.48</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18.05</v>
+        <v>180.49</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.02</v>
+        <v>170.19</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16.96</v>
+        <v>169.57</v>
       </c>
     </row>
     <row r="15">
@@ -789,7 +789,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.65</v>
+        <v>166.53</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16.05</v>
+        <v>160.54</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15.96</v>
+        <v>159.57</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.78</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.35</v>
+        <v>153.54</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15.21</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>15.02</v>
+        <v>150.21</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14.94</v>
+        <v>149.42</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>14.88</v>
+        <v>148.81</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>14.8</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>14.31</v>
+        <v>143.13</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>13.87</v>
+        <v>138.74</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>13.32</v>
+        <v>133.16</v>
       </c>
     </row>
     <row r="28">
@@ -1010,7 +1010,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>12.64</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12.41</v>
+        <v>124.13</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.05</v>
+        <v>120.47</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10.46</v>
+        <v>104.62</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:07</t>
+    <t xml:space="preserve">2026-10-05 07:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
